--- a/$FSLY/$FSLY-2026-08-11/$FSLY_Investment_Model_2026-08-11.xlsx
+++ b/$FSLY/$FSLY-2026-08-11/$FSLY_Investment_Model_2026-08-11.xlsx
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">Assigned at $20 (net ~$19.35) — $2,000 cash/contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Re-accumulates near 50-day SMA ($19.83) if the gap fully fades. Note: still above base DCF ($12.87) — size modestly.</t>
+    <t xml:space="preserve">Re-accumulates near 50-day SMA ($19.83) if the gap fully fades. Note: still above base DCF ($13.37) — size modestly.</t>
   </si>
   <si>
     <t xml:space="preserve">Primary action this quarter is on the SHARES (hold core / trim into strength above bull DCF) — see memo Verdict. Overlay is optional.</t>
